--- a/codespace/results/ch3_fw1_finalized_cluster_anova_table.xlsx
+++ b/codespace/results/ch3_fw1_finalized_cluster_anova_table.xlsx
@@ -477,17 +477,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>171.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>95.06</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>108.25</t>
+          <t>105.40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -497,12 +497,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.53 ± 0.14</t>
+          <t>0.05 ± 0.01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.33 ± 0.47</t>
+          <t>0.50 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -514,17 +514,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>84.35</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4.94 ± 0.17</t>
+          <t>0.58 ± 0.03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.00 ± 0.30</t>
+          <t>0.28 ± 0.03</t>
         </is>
       </c>
     </row>
@@ -551,17 +551,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>66.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.33 ± 0.11</t>
+          <t>0.65 ± 0.02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.62 ± 0.41</t>
+          <t>0.38 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -588,32 +588,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.21</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0022**</t>
+          <t>0.0027**</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.21 ± 0.08</t>
+          <t>0.02 ± 0.01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.10 ± 0.42</t>
+          <t>0.11 ± 0.04</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0135*</t>
+          <t>0.0165*</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.26 ± 0.07</t>
+          <t>0.03 ± 0.01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.81 ± 0.30</t>
+          <t>0.08 ± 0.03</t>
         </is>
       </c>
     </row>
@@ -662,106 +662,106 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>75.94</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0250*</t>
+          <t>0.0166*</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.25 ± 0.10</t>
+          <t>0.02 ± 0.01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.00 ± 0.47</t>
+          <t>0.10 ± 0.05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.27</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0540</t>
+          <t>0.0201*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.57 ± 0.16</t>
+          <t>0.20 ± 0.02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.30 ± 0.43</t>
+          <t>0.32 ± 0.07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>156.22</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0862</t>
+          <t>0.0415*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.14 ± 0.20</t>
+          <t>0.05 ± 0.01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.95 ± 0.55</t>
+          <t>0.13 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -773,32 +773,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.2349</t>
+          <t>0.2277</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.56 ± 0.12</t>
+          <t>0.05 ± 0.01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.29 ± 0.14</t>
+          <t>0.03 ± 0.01</t>
         </is>
       </c>
     </row>
@@ -810,32 +810,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.3153</t>
+          <t>0.2983</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.50 ± 0.15</t>
+          <t>0.05 ± 0.01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.23 ± 0.16</t>
+          <t>0.02 ± 0.01</t>
         </is>
       </c>
     </row>
@@ -847,123 +847,123 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.4051</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.16 ± 0.08</t>
+          <t>0.01 ± 0.01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.30 ± 0.19</t>
+          <t>0.03 ± 0.02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.5482</t>
+          <t>0.5162</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.06 ± 0.05</t>
+          <t>0.04 ± 0.01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.12 ± 0.12</t>
+          <t>0.07 ± 0.04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.5683</t>
+          <t>0.5642</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.45 ± 0.14</t>
+          <t>0.04 ± 0.01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.63 ± 0.35</t>
+          <t>0.03 ± 0.02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>48.96</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.5835</t>
+          <t>0.5850</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.45 ± 0.14</t>
+          <t>0.01 ± 0.00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.31 ± 0.18</t>
+          <t>0.01 ± 0.01</t>
         </is>
       </c>
     </row>
@@ -995,32 +995,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.49</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.7754</t>
+          <t>0.6677</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.76 ± 0.16</t>
+          <t>0.08 ± 0.02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.68 ± 0.26</t>
+          <t>0.06 ± 0.02</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>107.50</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.8155</t>
+          <t>0.9336</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.81 ± 0.21</t>
+          <t>0.08 ± 0.02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.91 ± 0.28</t>
+          <t>0.09 ± 0.02</t>
         </is>
       </c>
     </row>

--- a/codespace/results/ch3_fw1_finalized_cluster_anova_table.xlsx
+++ b/codespace/results/ch3_fw1_finalized_cluster_anova_table.xlsx
@@ -477,17 +477,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105.40</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,29 +502,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.50 ± 0.06</t>
+          <t>0.51 ± 0.07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>37.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,34 +534,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.58 ± 0.03</t>
+          <t>0.66 ± 0.02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.28 ± 0.03</t>
+          <t>0.34 ± 0.05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>23.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.65 ± 0.02</t>
+          <t>0.56 ± 0.03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.38 ± 0.05</t>
+          <t>0.29 ± 0.04</t>
         </is>
       </c>
     </row>
@@ -588,22 +588,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0027**</t>
+          <t>0.0008***</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -613,44 +613,44 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.11 ± 0.04</t>
+          <t>0.12 ± 0.05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0165*</t>
+          <t>0.0056**</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.03 ± 0.01</t>
+          <t>0.04 ± 0.01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.08 ± 0.03</t>
+          <t>0.15 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -662,22 +662,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0166*</t>
+          <t>0.0059**</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -687,81 +687,81 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.10 ± 0.05</t>
+          <t>0.12 ± 0.06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0201*</t>
+          <t>0.0126*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.20 ± 0.02</t>
+          <t>0.03 ± 0.01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.32 ± 0.07</t>
+          <t>0.09 ± 0.03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0415*</t>
+          <t>0.1473</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.05 ± 0.01</t>
+          <t>0.21 ± 0.02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.13 ± 0.05</t>
+          <t>0.29 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.2277</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -815,34 +815,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.2983</t>
+          <t>0.4640</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.05 ± 0.01</t>
+          <t>0.04 ± 0.01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.02 ± 0.01</t>
+          <t>0.07 ± 0.05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -852,54 +852,54 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.4851</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>0.01 ± 0.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>0.01 ± 0.01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.03 ± 0.02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.5162</t>
+          <t>0.5246</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.07 ± 0.04</t>
+          <t>0.03 ± 0.02</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.5642</t>
+          <t>0.5260</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.04 ± 0.01</t>
+          <t>0.05 ± 0.01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -953,37 +953,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.5850</t>
+          <t>0.5957</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.01 ± 0.00</t>
+          <t>0.07 ± 0.02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.01 ± 0.01</t>
+          <t>0.10 ± 0.03</t>
         </is>
       </c>
     </row>
@@ -1000,17 +1000,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.6677</t>
+          <t>0.6945</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1020,14 +1020,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.06 ± 0.02</t>
+          <t>0.07 ± 0.03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.9336</t>
+          <t>0.9099</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.08 ± 0.02</t>
+          <t>0.02 ± 0.01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.09 ± 0.02</t>
+          <t>0.02 ± 0.02</t>
         </is>
       </c>
     </row>
@@ -1072,10 +1072,10 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
